--- a/EKG_Kalite_Yönetim_Sistemi/90_NSA, MPA ve PPQ Hazırlık Araçları/02_Öz Değerlendirme ve Aksiyon Yönetimi/EKG-KLT-PLN-10_qsb_arti_oz_degerlendirme_ve_aksiyon_plani.xlsx
+++ b/EKG_Kalite_Yönetim_Sistemi/90_NSA, MPA ve PPQ Hazırlık Araçları/02_Öz Değerlendirme ve Aksiyon Yönetimi/EKG-KLT-PLN-10_qsb_arti_oz_degerlendirme_ve_aksiyon_plani.xlsx
@@ -830,7 +830,8 @@
   <pageSetup scale="100"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-KLT-PLN-10&amp;C&amp;"Arial,Regular"&amp;11QSB Artı Öz Değerlendirme ve Aksiyon Planı</oddHeader>
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.06.2026 | Revizyon: 09.09.2026
+Revizyon nedeni: QSB+ listesi iç hazırlık aracı olarak tanımlandı; müşteri kaynağı, kanıt ve aksiyon alanları eklendi.&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
 </file>